--- a/요약.xlsx
+++ b/요약.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\www\design-token\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1B4E11-9971-4833-8648-8D60F96167C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5096DF-5C07-4360-A6E0-4BB3501EFF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15720" xr2:uid="{1F424765-6347-43D4-B390-4B847501340A}"/>
+    <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F424765-6347-43D4-B390-4B847501340A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>어떤 기본 요소들을 정리할 것인지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -508,7 +508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C42B891C-63C9-4D47-B652-84CF229FA639}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -592,9 +592,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H25" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/요약.xlsx
+++ b/요약.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\www\design-token\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5096DF-5C07-4360-A6E0-4BB3501EFF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1406E2B7-D3CC-4266-91D7-29C7CDCF819D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F424765-6347-43D4-B390-4B847501340A}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>어떤 기본 요소들을 정리할 것인지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -118,6 +118,18 @@
   </si>
   <si>
     <t>구조를 어떻게 나눌 것인가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>primary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>secondary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tertiary</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -125,7 +137,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +150,15 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -164,8 +185,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,97 +535,115 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C42B891C-63C9-4D47-B652-84CF229FA639}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
+    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="31" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H25" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H32" t="s">
         <v>4</v>
       </c>
     </row>
